--- a/dataFoodCPI/UEMOA_completes.xlsx
+++ b/dataFoodCPI/UEMOA_completes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harold/DataAnalyctisandScience/Cointegration_Johansen_test/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harold/DataAnalyctisandScience/Cointegration_Johansen_test/dataFoodCPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B475EDA3-DD7A-3B43-B582-E05D51E9385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354CB31F-DD4F-5B43-ACAE-D7538C39C06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
   <si>
     <t>Month</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>Crude oil, WTI ($/bbl)</t>
+  </si>
+  <si>
+    <t>Months</t>
   </si>
 </sst>
 </file>
@@ -504,7 +507,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
